--- a/data/processed/Disposition.xlsx
+++ b/data/processed/Disposition.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adi/Desktop/CareerPlan/Gov Applications/Current Active Applications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adi/Desktop/Projects/KC_BA_POC/KC_CrimeAnalytics/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857E0BDA-71B7-1C44-B4D6-675A5FCD026B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BDFC73-2478-BD49-BA67-83A5E3F08693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{D05B6770-A43F-6645-84F2-A332C6AE5F7C}"/>
+    <workbookView xWindow="-34760" yWindow="6380" windowWidth="26200" windowHeight="16940" xr2:uid="{D05B6770-A43F-6645-84F2-A332C6AE5F7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Disposition" sheetId="1" r:id="rId1"/>
@@ -41,15 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Incident Report Required?</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -210,6 +201,15 @@
   </si>
   <si>
     <t>OUT OF SERVICE (Down Time FCRs)</t>
+  </si>
+  <si>
+    <t>Dis_Code</t>
+  </si>
+  <si>
+    <t>Dis_CodeDesc</t>
+  </si>
+  <si>
+    <t>Dis_IncidentReportReq</t>
   </si>
 </sst>
 </file>
@@ -258,10 +258,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,305 +608,306 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="88.83203125" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="98.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="B24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
